--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486900_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486900_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6948</v>
+        <v>2.2279</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1652</v>
+        <v>2.7279</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4704</v>
+        <v>-0.5</v>
       </c>
       <c r="G2" t="n">
         <v>2.1355</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6147</v>
+        <v>1.1478</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3515</v>
+        <v>0.9142</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2632</v>
+        <v>0.2336</v>
       </c>
       <c r="V2" t="n">
         <v>-2.2874</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8353</v>
+        <v>1.9029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6591</v>
+        <v>0.9342</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1762</v>
+        <v>0.9687</v>
       </c>
       <c r="G3" t="n">
         <v>0.7493</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2646</v>
+        <v>0.3322</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2558</v>
+        <v>0.0193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5204</v>
+        <v>0.3129</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4258</v>
+        <v>1.0049</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3871</v>
+        <v>1.9958</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9613</v>
+        <v>-0.991</v>
       </c>
       <c r="G4" t="n">
         <v>0.8904</v>
@@ -766,13 +766,13 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8907</v>
+        <v>0.4697</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8096</v>
+        <v>0.4183</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0514</v>
       </c>
       <c r="V4" t="n">
         <v>1.2875</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1235</v>
+        <v>0.6587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.546</v>
+        <v>0.6662</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4225</v>
+        <v>-0.0075</v>
       </c>
       <c r="G5" t="n">
         <v>1.3386</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0877</v>
+        <v>0.4475</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4298</v>
+        <v>0.55</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5175</v>
+        <v>-0.1025</v>
       </c>
       <c r="V5" t="n">
         <v>0.3101</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8358</v>
+        <v>-0.4496</v>
       </c>
       <c r="E6" t="n">
-        <v>1.286</v>
+        <v>1.7316</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1219</v>
+        <v>-2.1812</v>
       </c>
       <c r="G6" t="n">
         <v>1.3009</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9499</v>
+        <v>-0.5637</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5192</v>
+        <v>-0.0737</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4307</v>
+        <v>-0.49</v>
       </c>
       <c r="V6" t="n">
         <v>-2.0082</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2062</v>
+        <v>-2.2013</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8273</v>
+        <v>-0.9706</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3789</v>
+        <v>-1.2307</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1181</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2692</v>
+        <v>0.2741</v>
       </c>
       <c r="T7" t="n">
-        <v>0.244</v>
+        <v>0.1006</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0252</v>
+        <v>0.1734</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9093</v>
+        <v>-2.4423</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9798</v>
+        <v>-4.1274</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0705</v>
+        <v>1.6851</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8153</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4522</v>
+        <v>0.9193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2675</v>
+        <v>0.5848</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7198</v>
+        <v>0.3344</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5195</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0406</v>
+        <v>-2.7564</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6447</v>
+        <v>-2.3309</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3959</v>
+        <v>-0.4255</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7931</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1592</v>
+        <v>0.1249</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1899</v>
+        <v>0.1239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0307</v>
+        <v>0.001</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5339</v>
+        <v>-3.1344</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6187</v>
+        <v>-2.0414</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9152</v>
+        <v>-1.0931</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8606</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1953</v>
+        <v>0.5948</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0041</v>
+        <v>0.5732</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1994</v>
+        <v>0.0215</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8686</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0489</v>
+        <v>-3.6588</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5844</v>
+        <v>-4.55</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5355</v>
+        <v>0.8912</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5249</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7005</v>
+        <v>0.6896</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7014</v>
+        <v>0.333</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0009</v>
+        <v>0.3566</v>
       </c>
       <c r="V11" t="n">
         <v>2.078</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.4953</v>
+        <v>-8.8484</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.611499999999999</v>
+        <v>-5.964599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8839</v>
+        <v>-2.884</v>
       </c>
       <c r="G12" t="n">
         <v>-3.697300000000001</v>
@@ -1390,13 +1390,13 @@
         <v>10.2673</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7894</v>
+        <v>4.436199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.896999999999999</v>
+        <v>3.543600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8925</v>
+        <v>0.8922999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-3.426899999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8455</v>
+        <v>5.4864</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9411</v>
+        <v>2.1043</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9044</v>
+        <v>3.3821</v>
       </c>
       <c r="G13" t="n">
         <v>2.0355</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0235</v>
+        <v>0.6644</v>
       </c>
       <c r="T13" t="n">
-        <v>1.104</v>
+        <v>0.2672</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0804</v>
+        <v>0.3973</v>
       </c>
       <c r="V13" t="n">
         <v>0.9384</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2884</v>
+        <v>4.2395</v>
       </c>
       <c r="E14" t="n">
-        <v>2.644</v>
+        <v>2.4348</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6444</v>
+        <v>1.8048</v>
       </c>
       <c r="G14" t="n">
         <v>3.1728</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3743</v>
+        <v>0.3255</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1704</v>
+        <v>-0.0388</v>
       </c>
       <c r="U14" t="n">
-        <v>0.204</v>
+        <v>0.3643</v>
       </c>
       <c r="V14" t="n">
         <v>1.7679</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1328</v>
+        <v>3.2877</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7402</v>
+        <v>-0.833</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3926</v>
+        <v>4.1207</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3197</v>
+        <v>0.9136</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.7826</v>
+        <v>-0.4282</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4629</v>
+        <v>1.3418</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9578</v>
+        <v>-0.8212</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.2337</v>
+        <v>-0.7684</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2759</v>
+        <v>-0.0529</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3619</v>
+        <v>1.7348</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5489000000000001</v>
+        <v>0.3401</v>
       </c>
       <c r="O15" t="n">
-        <v>0.187</v>
+        <v>1.3947</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2389</v>
+        <v>0.2509</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7432</v>
+        <v>-0.2869</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5043</v>
+        <v>0.5377</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1868</v>
+        <v>0.4805</v>
       </c>
       <c r="W15" t="n">
-        <v>3.1868</v>
+        <v>0.4805</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.212</v>
+        <v>2.6028</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4606</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6726</v>
+        <v>1.9087</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9136</v>
+        <v>-2.3197</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4282</v>
+        <v>-3.7826</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3418</v>
+        <v>1.4629</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8212</v>
+        <v>-1.9578</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7684</v>
+        <v>-3.2337</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0529</v>
+        <v>1.2759</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7348</v>
+        <v>-0.3619</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3401</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3947</v>
+        <v>0.187</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8248</v>
+        <v>0.7089</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9145</v>
+        <v>0.6972</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0897</v>
+        <v>0.0118</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4805</v>
+        <v>3.1868</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4805</v>
+        <v>3.1868</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6193</v>
+        <v>1.3766</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4598</v>
+        <v>0.0065</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8405</v>
+        <v>1.3701</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8344</v>
+        <v>-0.8199</v>
       </c>
       <c r="H17" t="n">
-        <v>1.729</v>
+        <v>0.6909</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1054</v>
+        <v>-1.5108</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8676</v>
+        <v>-0.2894</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6702</v>
+        <v>1.4084</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1973</v>
+        <v>-1.6978</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0332</v>
+        <v>-0.5305</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9412</v>
+        <v>-0.7174</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.092</v>
+        <v>0.187</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6699000000000001</v>
+        <v>-0.401</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9413</v>
+        <v>-0.2481</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2715</v>
+        <v>-0.1529</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.117</v>
+        <v>2.5975</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>2.5975</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4247</v>
+        <v>0.9969</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7257</v>
+        <v>2.7276</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1504</v>
+        <v>-1.7307</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8199</v>
+        <v>1.8344</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6909</v>
+        <v>1.729</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5108</v>
+        <v>0.1054</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2894</v>
+        <v>2.8676</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4084</v>
+        <v>2.6702</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6978</v>
+        <v>0.1973</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5305</v>
+        <v>-1.0332</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7174</v>
+        <v>-0.9412</v>
       </c>
       <c r="O18" t="n">
-        <v>0.187</v>
+        <v>-0.092</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3529</v>
+        <v>0.0475</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9804</v>
+        <v>0.2091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3725</v>
+        <v>-0.1616</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5975</v>
+        <v>-2.117</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5975</v>
+        <v>-0.3491</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1211</v>
+        <v>0.2417</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1317</v>
+        <v>0.6529</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0107</v>
+        <v>-0.4113</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0843</v>
+        <v>1.7645</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0552</v>
+        <v>0.5515</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1395</v>
+        <v>1.2131</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.1799</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5485</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6315</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0843</v>
+        <v>0.5846</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0552</v>
+        <v>0.003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1395</v>
+        <v>0.5816</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2053</v>
+        <v>-0.5414</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1317</v>
+        <v>-0.527</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0736</v>
+        <v>-0.0144</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1262</v>
+        <v>-0.0249</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6529</v>
+        <v>0.8915</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7791</v>
+        <v>-0.9164</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7645</v>
+        <v>-0.1107</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5515</v>
+        <v>0.4866</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2131</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1799</v>
+        <v>0.6696</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5485</v>
+        <v>1.3145</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6315</v>
+        <v>-0.6449</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5846</v>
+        <v>-0.7803</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003</v>
+        <v>-0.8278</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5816</v>
+        <v>0.0475</v>
       </c>
       <c r="P20" t="n">
         <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>2.2588</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9093</v>
+        <v>-0.3516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.527</v>
+        <v>-0.314</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3823</v>
+        <v>-0.0376</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0082</v>
+        <v>-0.5893</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0082</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8879</v>
+        <v>-0.1211</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1593</v>
+        <v>-0.1317</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0472</v>
+        <v>0.0107</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1107</v>
+        <v>0.0843</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4866</v>
+        <v>-0.0552</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.1395</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6696</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3145</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6449</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7803</v>
+        <v>0.0843</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8278</v>
+        <v>-0.0552</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0475</v>
+        <v>0.1395</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2588</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2146</v>
+        <v>-0.2053</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0462</v>
+        <v>-0.1317</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1683</v>
+        <v>-0.0736</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4878</v>
+        <v>-0.9544</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6507</v>
+        <v>-3.3369</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1629</v>
+        <v>2.3825</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2861</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4152</v>
+        <v>0.1182</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1776</v>
+        <v>0.3973</v>
       </c>
       <c r="V22" t="n">
         <v>0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4044</v>
+        <v>-3.8465</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7448</v>
+        <v>-2.3263</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6597</v>
+        <v>-1.5202</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5714</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1739</v>
+        <v>-0.616</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6587</v>
+        <v>-0.2403</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5152</v>
+        <v>-0.3757</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0698</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.4953</v>
+        <v>13.2847</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8838</v>
+        <v>2.883799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>7.6115</v>
+        <v>10.401</v>
       </c>
       <c r="G24" t="n">
         <v>3.697299999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5667999999999995</v>
+        <v>0.5668</v>
       </c>
       <c r="I24" t="n">
-        <v>3.130600000000002</v>
+        <v>3.130600000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>2.583800000000001</v>
+        <v>2.5838</v>
       </c>
       <c r="K24" t="n">
         <v>3.2963</v>
@@ -2326,13 +2326,13 @@
         <v>16.4275</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7894</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8924</v>
+        <v>-0.8922999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.8968</v>
+        <v>0.8926000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>3.427</v>
